--- a/docs/초기_진행문서/db/Garim_DB_Design_final_clean_v13.xlsx
+++ b/docs/초기_진행문서/db/Garim_DB_Design_final_clean_v13.xlsx
@@ -168,7 +168,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
@@ -337,6 +337,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -22596,7 +22599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="3"/>
@@ -23106,81 +23109,77 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="28.5" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>취소 요청 여부</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>cancel_requested</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
-        <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="inlineStr">
-        <is>
-          <t>사용자가 취소를 누른 뒤 워커가 안전 중단해야 하는지 표시</t>
+    <row r="16">
+      <c r="A16" s="58" t="inlineStr">
+        <is>
+          <t>대상 PII ID</t>
+        </is>
+      </c>
+      <c r="B16" s="58" t="inlineStr">
+        <is>
+          <t>target_pii_id</t>
+        </is>
+      </c>
+      <c r="C16" s="58" t="inlineStr">
+        <is>
+          <t>varchar(100)</t>
+        </is>
+      </c>
+      <c r="D16" s="58" t="n"/>
+      <c r="E16" s="58" t="n"/>
+      <c r="F16" s="58" t="n"/>
+      <c r="G16" s="58" t="n"/>
+      <c r="H16" s="58" t="n"/>
+      <c r="I16" s="58" t="inlineStr">
+        <is>
+          <t>마스킹 미리보기/본처리 작업에서 단일 PII를 지정하기 위한 식별자. null이면 사용자 선택 전체 대상</t>
         </is>
       </c>
     </row>
     <row r="17" ht="42.75" customHeight="1">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>원본 길이 초</t>
+          <t>취소 요청 여부</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>duration_seconds</t>
+          <t>cancel_requested</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
       <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="inlineStr">
-        <is>
-          <t>check (duration_seconds &gt;= 0)</t>
-        </is>
-      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>영상 원본 길이 초</t>
+          <t>사용자가 취소를 누른 뒤 워커가 안전 중단해야 하는지 표시</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>원본 너비</t>
+          <t>원본 길이 초</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>width</t>
+          <t>duration_seconds</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -23194,24 +23193,24 @@
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>check (width &gt;= 0)</t>
+          <t>check (duration_seconds &gt;= 0)</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>원본 영상/이미지 너비</t>
+          <t>영상 원본 길이 초</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>원본 높이</t>
+          <t>원본 너비</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>width</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -23225,24 +23224,24 @@
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>check (height &gt;= 0)</t>
+          <t>check (width &gt;= 0)</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>원본 영상/이미지 높이</t>
+          <t>원본 영상/이미지 너비</t>
         </is>
       </c>
     </row>
     <row r="20" ht="42.75" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>탐지 개수</t>
+          <t>원본 높이</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>detection_count</t>
+          <t>height</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -23252,68 +23251,72 @@
       </c>
       <c r="D20" s="12" t="n"/>
       <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>check (detection_count &gt;= 0)</t>
+          <t>check (height &gt;= 0)</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>리포트/목록 재집계를 줄이기 위한 검출 건수 캐시</t>
+          <t>원본 영상/이미지 높이</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>오류 코드</t>
+          <t>탐지 개수</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>error_code</t>
+          <t>detection_count</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>varchar(100)</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D21" s="12" t="n"/>
       <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>check (detection_count &gt;= 0)</t>
+        </is>
+      </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>실패 원인을 시스템적으로 분류하는 코드</t>
+          <t>리포트/목록 재집계를 줄이기 위한 검출 건수 캐시</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>오류 메시지</t>
+          <t>오류 코드</t>
         </is>
       </c>
       <c r="B22" s="12" t="inlineStr">
         <is>
-          <t>error_message</t>
+          <t>error_code</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>varchar(100)</t>
         </is>
       </c>
       <c r="D22" s="12" t="n"/>
@@ -23323,19 +23326,19 @@
       <c r="H22" s="12" t="n"/>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>사용자 또는 관리자에게 보여줄 상세 설명</t>
+          <t>실패 원인을 시스템적으로 분류하는 코드</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28.5" customHeight="1">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>결과 파일 경로</t>
+          <t>오류 메시지</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>result_file_path</t>
+          <t>error_message</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -23350,81 +23353,81 @@
       <c r="H23" s="12" t="n"/>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>처리 완료 결과 파일 또는 내부 스토리지 경로</t>
+          <t>사용자 또는 관리자에게 보여줄 상세 설명</t>
         </is>
       </c>
     </row>
     <row r="24" ht="85.5" customHeight="1">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>리포트 ID</t>
+          <t>결과 파일 경로</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>report_id</t>
+          <t>result_file_path</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>uuid</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="E24" s="12" t="n"/>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="inlineStr">
-        <is>
-          <t>references analysis_artifacts(artifact_id) 또는 reports(report_id), 실제 구현 기준 FK 선택</t>
-        </is>
-      </c>
+      <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>분석 리포트/아티팩트 연결</t>
+          <t>처리 완료 결과 파일 또는 내부 스토리지 경로</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>시작 일시</t>
+          <t>리포트 ID</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>started_at</t>
+          <t>report_id</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>uuid</t>
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
+      <c r="E25" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
+      <c r="H25" s="12" t="inlineStr">
+        <is>
+          <t>references analysis_artifacts(artifact_id) 또는 reports(report_id), 실제 구현 기준 FK 선택</t>
+        </is>
+      </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>작업 시작 시각</t>
+          <t>분석 리포트/아티팩트 연결</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>완료 일시</t>
+          <t>시작 일시</t>
         </is>
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>completed_at</t>
+          <t>started_at</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
@@ -23439,19 +23442,19 @@
       <c r="H26" s="12" t="n"/>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>작업 완료 시각</t>
+          <t>작업 시작 시각</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>등록 일시</t>
+          <t>완료 일시</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>completed_at</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
@@ -23461,32 +23464,24 @@
       </c>
       <c r="D27" s="12" t="n"/>
       <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>now()</t>
-        </is>
-      </c>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
       <c r="H27" s="12" t="n"/>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>레코드가 생성된 시각</t>
+          <t>작업 완료 시각</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>수정 일시</t>
+          <t>등록 일시</t>
         </is>
       </c>
       <c r="B28" s="12" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -23508,6 +23503,41 @@
       </c>
       <c r="H28" s="12" t="n"/>
       <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>레코드가 생성된 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>수정 일시</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>now()</t>
+        </is>
+      </c>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="inlineStr">
         <is>
           <t>레코드가 마지막으로 수정된 시각</t>
         </is>
